--- a/extenbooks/S1701_extenbook.xlsx
+++ b/extenbooks/S1701_extenbook.xlsx
@@ -14882,7 +14882,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -16178,11 +16178,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16205,76 +16205,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Global Crisis 2007 in light of Past Long Waves (Fig 17.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1701_research.json", "adequacy_report": "Technical/docs/chapters/CH17_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1701_DPR.md", "epr": "Technical/docs/series/S1701_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1701_load.py", "processor": "Technical/code/P02_processors/P02_S1701_construct.py", "validator": "Technical/code/V03_validators/V03_S1701_validate.py", "processed": "Technical/data/processed/S1701.parquet", "chopped_csv": "Technical/chopped/S1701.csv"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:56:16.880881+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1701_extenbook.xlsx
+++ b/extenbooks/S1701_extenbook.xlsx
@@ -14829,7 +14829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A162"/>
+  <dimension ref="A1:A166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -14868,79 +14868,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Series ID**: S1701</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Series ID**: S1701</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>## 1. Definition</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>## 1. Definition</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>US and UK wholesale price indexes (WPI) expressed in ounces of gold,</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HP-smoothed (lambda=100) US and UK wholesale price indexes expressed in</t>
+          <t>smoothed with a Hodrick-Prescott filter (smoothing parameter 100), plus the</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ounces of gold, plus the average-of-past-two-waves overlay used to project</t>
+          <t>average-of-past-two-waves overlay used to project the 2008-2018 crisis.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>the 2008-2018 crisis. Appears in Shaikh (2016) as **Figure 17.1** (p. 749);</t>
+          <t>Appears in Shaikh (2016) as **Figure 17.1** (p. 749); reuses the data already</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reuses the data already plotted as Fig 16.1.</t>
+          <t>plotted as Fig 16.1.</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Three subseries:</t>
+          <t>Three component subseries (labelled -A, -B, -C):</t>
         </is>
       </c>
     </row>
@@ -15046,21 +15046,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| S1701-A | Appendix5_DATALRprices.xlsx | USPPIGOLDHP100 | 1800-2007 |</t>
+          <t>| S1701-A | Chapter 5 appendix data tables (Shaikh 2016, App. 5.3) | USPPIGOLDHP100 | 1800-2007 |</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| S1701-B | Appendix5_DATALRprices.xlsx | UKPPIGOLDHP100 | 1801-2007 |</t>
+          <t>| S1701-B | Chapter 5 appendix data tables (Shaikh 2016, App. 5.3) | UKPPIGOLDHP100 | 1801-2007 |</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| S1701-C | Appendix5_DATALRprices.xlsx | USUKAVGWAVE | 1983-2025 |</t>
+          <t>| S1701-C | Chapter 5 appendix data tables (Shaikh 2016, App. 5.3) | USUKAVGWAVE | 1983-2025 |</t>
         </is>
       </c>
     </row>
@@ -15070,202 +15070,206 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Per Phase 4 CH17 adequacy, `anwarshaikhecon.org` (the originally cited URL)</t>
+          <t>The originally cited URL `anwarshaikhecon.org` no longer resolves; the local</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DNS no longer resolves; the local salvage file IS canonical, with IA snapshot</t>
+          <t>salvage copy of the appendix data IS canonical, with an Internet Archive</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>`https://web.archive.org/web/20240311145229/https://www.anwarshaikhecon.org/`</t>
+          <t>snapshot</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>`https://web.archive.org/web/20240311145229/https://www.anwarshaikhecon.org/`</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>recorded as web citation.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>## 4. Construction</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>`composite`. Pass-through of three workbook columns; no algebraic combination.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>- S1701-A 1800-2007 (208 yrs); S1701-B 1801-2007 (218 yrs incl. early UK);</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1701-C 1983-2025 (43 yrs; 2012+ is forecast).</t>
+          <t>- S1701-A 1800-2007 (208 yrs); S1701-B 1801-2007 (218 yrs incl. early UK);</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>- Phase 4 CH17 recommendation: split the dashed overlay into data + forecast</t>
+          <t xml:space="preserve">  S1701-C 1983-2025 (43 yrs; 2012+ is forecast).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  layers — implemented as `is_forecast: True` flag on post-2011 rows.</t>
+          <t>- The dashed overlay is split into data + forecast layers — implemented as</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  an `is_forecast: True` flag on post-2011 rows.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>## 6. Units</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>`index_dimensionless_HP100_smoothed`.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-    </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1. **Series stub-vs-figure rename ratified.** CD2 S102 was the IRS table;</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Fig 17.1 is the long-wave chart. Phase 4 renamed S1701 to match the figure;</t>
+          <t>1. **Series stub-vs-figure rename.** An earlier replication assigned the</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">   IRS lineage captured in S1702/S1703.</t>
+          <t xml:space="preserve">   identifier S102 to the IRS table; Fig 17.1 is the long-wave chart. S1701</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2. **HP-filter padding undocumented in Shaikh.** Boundary-year smoothing</t>
+          <t xml:space="preserve">   was renamed to match the figure; IRS lineage captured in S1702/S1703.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">   choices depend on padding method; we use the workbook's stored values</t>
+          <t>2. **HP-filter padding undocumented in Shaikh.** Boundary-year smoothing</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">   verbatim and do not re-smooth.</t>
+          <t xml:space="preserve">   choices depend on padding method; we use the workbook's stored values</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3. **Forecast layer.** Post-2011 USUKAVGWAVE values are Shaikh's projection,</t>
+          <t xml:space="preserve">   verbatim and do not re-smooth.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">   not data; preserved with `is_forecast` flag.</t>
+          <t>3. **Forecast layer.** Post-2011 USUKAVGWAVE values are Shaikh's projection,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4. **MeasuringWorth WPI extension URL is dead** (Phase 4 CH17, returned 404).</t>
+          <t xml:space="preserve">   not data; preserved with `is_forecast` flag.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Substitute NBER m04051a + BLS WPU00000000 documented but not implemented v1.</t>
+          <t>4. **MeasuringWorth WPI extension URL is dead** (returned 404). Substitute</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   National Bureau of Economic Research (NBER) m04051a + BLS WPU00000000</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t xml:space="preserve">   documented but not implemented in v1.</t>
         </is>
       </c>
     </row>
@@ -15275,31 +15279,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>- CD legacy: S102 (name-mismatch — Phase 4 rename); CD2 legacy: S102</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>- Book: Shaikh (2016) p. 749 (figure), 900 (Appendix 17.1 method)</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>- Companion: Fig 16.1 uses the same input columns</t>
+          <t>- Earlier replications used the identifier S102 (renamed here to match the figure)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- Book: Shaikh (2016) p. 749 (figure), 900 (Appendix 17.1 method)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- Companion: Fig 16.1 uses the same input columns</t>
         </is>
       </c>
     </row>
@@ -15309,119 +15313,119 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>Tolerance ±0.5%. Achieved: MAE 0.0, max 0.0%, n=469. PASS.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="4">
+    <row r="87">
+      <c r="A87" s="4">
         <f>== EPR: S1701_EPR.md ===</f>
         <v/>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t># S1701 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t># S1701 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>**Construction**: `composite` (three independent overlay lines)</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>**Extension method**: re-compute WPI-in-gold from extended WPI + extended gold price; re-apply HP(100)</t>
+          <t>**Construction**: `composite` (three independent overlay lines)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Status v1**: `deferred` — book period emitted, post-2007 recomposition deferred to Phase 9</t>
+          <t>**Extension method**: re-compute WPI-in-gold from extended WPI + extended gold price; re-apply HP(100)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>**Status v1**: `deferred` — book period emitted, post-2007 recomposition deferred to a later revision</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-    </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>## 1. Why this series is extendable (but requires recomposition, not splice)</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-    </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>S1701-A and S1701-B are HP-100-smoothed derived quantities. Per anu-framework</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>No-Lazy-Splices-on-Derived-Quantities rule, extension MUST recompute the WPI</t>
+          <t>S1701-A and S1701-B are Hodrick-Prescott-smoothed (smoothing parameter 100)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>in gold from extended raw WPI + extended gold price, then re-apply HP(100).</t>
+          <t>derived quantities. Because these are smoothed/derived quantities, any</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Growth-rate splice on the smoothed series itself is prohibited.</t>
+          <t>extension must recompute the wholesale price index (WPI) in gold from extended</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>raw WPI + extended gold price, then re-apply HP(100), rather than splicing the</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S1701-C (USUKAVGWAVE) is itself derived from S1701-A/B via averaging across</t>
+          <t>smoothed series directly. Growth-rate splice on the smoothed series itself is</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>the two completed long waves; its extension is computed analogously.</t>
+          <t>prohibited.</t>
         </is>
       </c>
     </row>
@@ -15431,279 +15435,279 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>## 2. Concept Match Justifications (Phase 9 extension)</t>
+          <t>S1701-C (USUKAVGWAVE) is itself derived from S1701-A/B via averaging across</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>the two completed long waves; its extension is computed analogously.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>### US WPI input substitution</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>- Original: MeasuringWorth "Annual WPI for US 1720-Present" (URL 404 as of</t>
+          <t>## 2. Concept Match Justifications (planned extension)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2026-05-18; dataset no longer published).</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>- Substitute: NBER macrohistory Warren-Pearson m04051a series (pre-1947)</t>
+          <t>### US WPI input substitution</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  spliced to BLS WPU00000000 (post-1947). Same bridge used for Ch5 S502/S504.</t>
+          <t>- Original: MeasuringWorth "Annual WPI for US 1720-Present" (URL 404 as of</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>- Concept match: both measure the wholesale price level of US tradable goods;</t>
+          <t xml:space="preserve">  2026-05-18; dataset no longer published).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Warren-Pearson is the pre-1947 standard, WPU00000000 is the BLS successor</t>
+          <t>- Substitute: National Bureau of Economic Research (NBER) macrohistory Warren-Pearson m04051a series (pre-1947)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  series. Concept-exact (same agency lineage).</t>
+          <t xml:space="preserve">  spliced to BLS WPU00000000 (post-1947). Same bridge used for Ch5 S502/S504.</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>- Concept match: both measure the wholesale price level of US tradable goods;</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>### Gold price input</t>
+          <t xml:space="preserve">  Warren-Pearson is the pre-1947 standard, WPU00000000 is the BLS successor</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>- MeasuringWorth "Price of Gold, 1257-Present"</t>
+          <t xml:space="preserve">  series. Concept-exact (same agency lineage).</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (`https://www.measuringworth.com/datasets/gold/`, verified 200 OK).</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>- Concept-exact.</t>
+          <t>### Gold price input</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>- MeasuringWorth "Price of Gold, 1257-Present"</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>### UK WPI input</t>
+          <t xml:space="preserve">  (`https://www.measuringworth.com/datasets/gold/`, verified 200 OK).</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>- BoE "A Millennium of Macroeconomic Data" (Sally Hills, Ryland Thomas,</t>
+          <t>- Concept-exact.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nicholas Dimsdale) at `https://www.bankofengland.co.uk/statistics/research-datasets`</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (verified 200 OK).</t>
+          <t>### UK WPI input</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>- Concept match acceptable; overlap-anchor in 1960s-70s window before</t>
+          <t>- Bank of England (BoE) "A Millennium of Macroeconomic Data" (Sally Hills, Ryland Thomas,</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">  recomposition.</t>
+          <t xml:space="preserve">  Nicholas Dimsdale) at `https://www.bankofengland.co.uk/statistics/research-datasets`</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (verified 200 OK).</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>## 3. Method (planned, v1 = deferred)</t>
+          <t>- Concept match acceptable; overlap-anchor in 1960s-70s window before</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  recomposition.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>For each country c in {US, UK}:</t>
+          <t>## 3. Method (planned, v1 = deferred)</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WPI[c, year]  = extended WPI series spliced to Shaikh's</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">    gold[c, year] = MeasuringWorth gold price in c's currency</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WPI_in_gold[c, year] = WPI[c,year] / gold[c, year]</t>
+          <t>For each country c in {US, UK}:</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Re-apply HP(100) over the full extended range</t>
+          <t xml:space="preserve">    WPI[c, year]  = extended WPI series spliced to Shaikh's</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>USUKAVGWAVE[year] = mean over the two long-wave intervals projected forward</t>
+          <t xml:space="preserve">    gold[c, year] = MeasuringWorth gold price in c's currency</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    (forecast layer; preserve is_forecast flag)</t>
+          <t xml:space="preserve">    WPI_in_gold[c, year] = WPI[c,year] / gold[c, year]</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">    Re-apply HP(100) over the full extended range</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>USUKAVGWAVE[year] = mean over the two long-wave intervals projected forward</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy compliance</t>
+          <t xml:space="preserve">                    (forecast layer; preserve is_forecast flag)</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>US WPI substitution is concept-exact (NBER+BLS bridge). UK WPI substitution</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>acceptable (BoE Millennium). Both flagged `proxy: false` if Phase 9 uses</t>
+          <t>## 4. Source substitutions</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>identical concept; flagged `proxy: true` only if a different concept is used.</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>US WPI substitution is concept-exact (NBER+BLS bridge). UK WPI substitution</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic compliance</t>
+          <t>acceptable (BoE Millennium). Both flagged `proxy: false` if the extension uses</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>identical concept; flagged `proxy: true` only if a different concept is used.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Forecast portion of USUKAVGWAVE is preserved as `is_forecast: True`. Never</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>imputed; values come directly from Shaikh's projection.</t>
+          <t>## 5. Forecast vs. observed data</t>
         </is>
       </c>
     </row>
@@ -15713,72 +15717,96 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>Forecast portion of USUKAVGWAVE is preserved as `is_forecast: True`. Never</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>imputed; values come directly from Shaikh's projection.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>| Failure | Action |</t>
-        </is>
-      </c>
+      <c r="A153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>| NBER macrohistory unavailable | Use BLS WPU00000000 from 1947 only |</t>
-        </is>
-      </c>
+      <c r="A155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>| BLS WPU unavailable | Mark US extension `api_unavailable` |</t>
+          <t>| Failure | Action |</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>| BoE Millennium not refreshed | UK extension capped at last available |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>| NBER macrohistory unavailable | Use BLS WPU00000000 from 1947 only |</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>| BLS WPU unavailable | Mark US extension `api_unavailable` |</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>| BoE Millennium not refreshed | UK extension capped at last available |</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>CD2's S102 was misnamed (IRS table); RSCD reassigned the long-wave figure</t>
-        </is>
-      </c>
+      <c r="A161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>to S1701. v1 reproduces the Appendix 5.3 spreadsheet columns exactly.</t>
+          <t>## 7. Divergence from earlier replications</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>An earlier replication assigned S102 to the IRS table; RSCD reassigned the</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>long-wave figure to S1701. v1 reproduces the Appendix 5.3 spreadsheet columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>exactly.</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16080,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -16163,7 +16191,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T23:11:54.618520+00:00</t>
+          <t>2026-07-02T06:20:37.236298+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1701_extenbook.xlsx
+++ b/extenbooks/S1701_extenbook.xlsx
@@ -16191,7 +16191,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:20:37.236298+00:00</t>
+          <t>2026-07-11T03:44:23.912718+00:00</t>
         </is>
       </c>
     </row>
@@ -16206,11 +16206,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16233,6 +16233,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_5_3_DATALRPRICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "fix-completed-then-publish", "reason": "HALLUCINATED NAME CORRECTED: registry name field carried stale CD2 S102 inheritance 'IRS 2011 Income Distribution \u2014 Full Table'; the Phase-4 rename was logged in name_history but never applied. Chopped data (gold-price HP-100 long waves, 1790+) and KB figure 17.1 caption confirm the long-waves identity. Registry name + figures fixed; generator _phase5_ch11_13_17_register.py patched to emit name+figures. Verbatim quotes match.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1701_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1701_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 17.1; renamed Phase 4; IRS lineage captured in S1702/S1703.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>index_dimensionless_HP100_smoothed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
